--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -1601,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129944831</v>
+        <v>129944905</v>
       </c>
       <c r="B10" t="n">
-        <v>57895</v>
+        <v>57734</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,27 +1612,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1641,13 +1641,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521008</v>
+        <v>520994</v>
       </c>
       <c r="R10" t="n">
-        <v>6625737</v>
+        <v>6625626</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,31 +1697,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129944905</v>
+        <v>129944831</v>
       </c>
       <c r="B11" t="n">
-        <v>57734</v>
+        <v>57895</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,27 +1724,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1758,13 +1753,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520994</v>
+        <v>521008</v>
       </c>
       <c r="R11" t="n">
-        <v>6625626</v>
+        <v>6625737</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1793,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,16 +1809,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129944723</v>
       </c>
       <c r="B2" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>129944923</v>
       </c>
       <c r="B3" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>129944586</v>
       </c>
       <c r="B4" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>129944799</v>
       </c>
       <c r="B5" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>129944648</v>
       </c>
       <c r="B6" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>129944497</v>
       </c>
       <c r="B7" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>129944527</v>
       </c>
       <c r="B8" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>129944883</v>
       </c>
       <c r="B9" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>129944905</v>
       </c>
       <c r="B10" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>129944831</v>
       </c>
       <c r="B11" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>129945020</v>
       </c>
       <c r="B12" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>129944853</v>
       </c>
       <c r="B13" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129944867</v>
       </c>
       <c r="B14" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>129944637</v>
       </c>
       <c r="B15" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -1601,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129944905</v>
+        <v>129944831</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>57898</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,27 +1612,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1641,13 +1641,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520994</v>
+        <v>521008</v>
       </c>
       <c r="R10" t="n">
-        <v>6625626</v>
+        <v>6625737</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,26 +1697,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129944831</v>
+        <v>129944905</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,27 +1729,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1753,13 +1758,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521008</v>
+        <v>520994</v>
       </c>
       <c r="R11" t="n">
-        <v>6625737</v>
+        <v>6625626</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1788,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1803,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,21 +1814,16 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129944723</v>
       </c>
       <c r="B2" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>129944923</v>
       </c>
       <c r="B3" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>129944586</v>
       </c>
       <c r="B4" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>129944799</v>
       </c>
       <c r="B5" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>129944648</v>
       </c>
       <c r="B6" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>129944497</v>
       </c>
       <c r="B7" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>129944883</v>
       </c>
       <c r="B9" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129944831</v>
+        <v>129944905</v>
       </c>
       <c r="B10" t="n">
-        <v>57898</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,27 +1612,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1641,13 +1641,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521008</v>
+        <v>520994</v>
       </c>
       <c r="R10" t="n">
-        <v>6625737</v>
+        <v>6625626</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,31 +1697,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129944905</v>
+        <v>129944831</v>
       </c>
       <c r="B11" t="n">
-        <v>57737</v>
+        <v>57898</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,27 +1724,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1758,13 +1753,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520994</v>
+        <v>521008</v>
       </c>
       <c r="R11" t="n">
-        <v>6625626</v>
+        <v>6625737</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1793,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,16 +1809,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1949,7 +1949,7 @@
         <v>129944853</v>
       </c>
       <c r="B13" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129944723</v>
       </c>
       <c r="B2" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>129944923</v>
       </c>
       <c r="B3" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>129944586</v>
       </c>
       <c r="B4" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>129944799</v>
       </c>
       <c r="B5" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>129944648</v>
       </c>
       <c r="B6" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>129944497</v>
       </c>
       <c r="B7" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>129944883</v>
       </c>
       <c r="B9" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>129944831</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>129944853</v>
       </c>
       <c r="B13" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129944867</v>
       </c>
       <c r="B14" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129944723</v>
       </c>
       <c r="B2" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>129944923</v>
       </c>
       <c r="B3" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>129944586</v>
       </c>
       <c r="B4" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>129944799</v>
       </c>
       <c r="B5" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>129944648</v>
       </c>
       <c r="B6" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>129944497</v>
       </c>
       <c r="B7" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>129944883</v>
       </c>
       <c r="B9" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>129944853</v>
       </c>
       <c r="B13" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>130112840</v>
       </c>
       <c r="B17" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>130112687</v>
       </c>
       <c r="B18" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2642,53 +2642,60 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130112479</v>
+        <v>130116668</v>
       </c>
       <c r="B19" t="n">
-        <v>58113</v>
+        <v>98833</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bråtbäcken, Bråtbäcken, Vstm</t>
+          <t>Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520967</v>
+        <v>521036</v>
       </c>
       <c r="R19" t="n">
-        <v>6625775</v>
+        <v>6625624</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2715,19 +2722,14 @@
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:18</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2736,83 +2738,72 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130116668</v>
+        <v>130112479</v>
       </c>
       <c r="B20" t="n">
-        <v>98831</v>
+        <v>58113</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bäckmossen, Vstm</t>
+          <t>Bråtbäcken, Bråtbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521036</v>
+        <v>520967</v>
       </c>
       <c r="R20" t="n">
-        <v>6625624</v>
+        <v>6625775</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2839,14 +2830,19 @@
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>30 plantor</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2855,19 +2851,23 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3204,7 +3204,7 @@
         <v>130129396</v>
       </c>
       <c r="B24" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>130112362</v>
       </c>
       <c r="B25" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129944723</v>
       </c>
       <c r="B2" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>129944923</v>
       </c>
       <c r="B3" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>129944586</v>
       </c>
       <c r="B4" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>129944799</v>
       </c>
       <c r="B5" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>129944648</v>
       </c>
       <c r="B6" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>129944497</v>
       </c>
       <c r="B7" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>129944527</v>
       </c>
       <c r="B8" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>129944883</v>
       </c>
       <c r="B9" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>129944905</v>
       </c>
       <c r="B10" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>129944831</v>
       </c>
       <c r="B11" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>129945020</v>
       </c>
       <c r="B12" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>129944853</v>
       </c>
       <c r="B13" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129944867</v>
       </c>
       <c r="B14" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>129944637</v>
       </c>
       <c r="B15" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>130116665</v>
       </c>
       <c r="B16" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>130112840</v>
       </c>
       <c r="B17" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>130112687</v>
       </c>
       <c r="B18" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2642,60 +2642,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130116668</v>
+        <v>130112479</v>
       </c>
       <c r="B19" t="n">
-        <v>98833</v>
+        <v>58198</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bäckmossen, Vstm</t>
+          <t>Bråtbäcken, Bråtbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521036</v>
+        <v>520967</v>
       </c>
       <c r="R19" t="n">
-        <v>6625624</v>
+        <v>6625775</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2722,14 +2715,19 @@
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>30 plantor</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,72 +2736,83 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130112479</v>
+        <v>130116668</v>
       </c>
       <c r="B20" t="n">
-        <v>58113</v>
+        <v>98920</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bråtbäcken, Bråtbäcken, Vstm</t>
+          <t>Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520967</v>
+        <v>521036</v>
       </c>
       <c r="R20" t="n">
-        <v>6625775</v>
+        <v>6625624</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2830,19 +2839,14 @@
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:18</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2851,23 +2855,19 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2877,7 +2877,7 @@
         <v>130116663</v>
       </c>
       <c r="B21" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>130116664</v>
       </c>
       <c r="B22" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>130116662</v>
       </c>
       <c r="B23" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>130129396</v>
       </c>
       <c r="B24" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>130112362</v>
       </c>
       <c r="B25" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2642,53 +2642,60 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130112479</v>
+        <v>130116668</v>
       </c>
       <c r="B19" t="n">
-        <v>58198</v>
+        <v>98920</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bråtbäcken, Bråtbäcken, Vstm</t>
+          <t>Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520967</v>
+        <v>521036</v>
       </c>
       <c r="R19" t="n">
-        <v>6625775</v>
+        <v>6625624</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2715,19 +2722,14 @@
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:18</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2736,83 +2738,72 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130116668</v>
+        <v>130112479</v>
       </c>
       <c r="B20" t="n">
-        <v>98920</v>
+        <v>58198</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bäckmossen, Vstm</t>
+          <t>Bråtbäcken, Bråtbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521036</v>
+        <v>520967</v>
       </c>
       <c r="R20" t="n">
-        <v>6625624</v>
+        <v>6625775</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2839,14 +2830,19 @@
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>30 plantor</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2855,19 +2851,23 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3412,6 +3412,248 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130113009</v>
+      </c>
+      <c r="B26" t="n">
+        <v>105987</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bäckmossen, Bäckmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>520995</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6625696</v>
+      </c>
+      <c r="S26" t="n">
+        <v>36</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anneli Sjöstrand</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anneli Sjöstrand</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130112471</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98920</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bäckmossen, Bäckmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>520995</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6625696</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anneli Sjöstrand</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anneli Sjöstrand</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129944799</v>
+        <v>129944497</v>
       </c>
       <c r="B5" t="n">
         <v>98920</v>
@@ -1052,26 +1052,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bäckmossen, Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521050</v>
+        <v>521096</v>
       </c>
       <c r="R5" t="n">
-        <v>6625624</v>
+        <v>6625627</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,7 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,7 +1131,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129944648</v>
+        <v>129944799</v>
       </c>
       <c r="B6" t="n">
         <v>98920</v>
@@ -1170,7 +1161,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1178,21 +1169,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bäckmossen, Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521069</v>
+        <v>521050</v>
       </c>
       <c r="R6" t="n">
-        <v>6625634</v>
+        <v>6625624</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,7 +1247,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129944497</v>
+        <v>129944648</v>
       </c>
       <c r="B7" t="n">
         <v>98920</v>
@@ -1289,17 +1275,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bäckmossen, Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521096</v>
+        <v>521069</v>
       </c>
       <c r="R7" t="n">
-        <v>6625627</v>
+        <v>6625634</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -1024,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129944497</v>
+        <v>129944799</v>
       </c>
       <c r="B5" t="n">
         <v>98920</v>
@@ -1052,17 +1052,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bäckmossen, Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521096</v>
+        <v>521050</v>
       </c>
       <c r="R5" t="n">
-        <v>6625627</v>
+        <v>6625624</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1103,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1113,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,7 +1140,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129944799</v>
+        <v>129944648</v>
       </c>
       <c r="B6" t="n">
         <v>98920</v>
@@ -1161,7 +1170,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1169,16 +1178,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bäckmossen, Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521050</v>
+        <v>521069</v>
       </c>
       <c r="R6" t="n">
-        <v>6625624</v>
+        <v>6625634</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,7 +1261,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129944648</v>
+        <v>129944497</v>
       </c>
       <c r="B7" t="n">
         <v>98920</v>
@@ -1275,31 +1289,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bäckmossen, Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521069</v>
+        <v>521096</v>
       </c>
       <c r="R7" t="n">
-        <v>6625634</v>
+        <v>6625627</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2642,60 +2642,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130116668</v>
+        <v>130112479</v>
       </c>
       <c r="B19" t="n">
-        <v>98920</v>
+        <v>58198</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bäckmossen, Vstm</t>
+          <t>Bråtbäcken, Bråtbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521036</v>
+        <v>520967</v>
       </c>
       <c r="R19" t="n">
-        <v>6625624</v>
+        <v>6625775</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2722,14 +2715,19 @@
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>30 plantor</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,72 +2736,83 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130112479</v>
+        <v>130116668</v>
       </c>
       <c r="B20" t="n">
-        <v>58198</v>
+        <v>98920</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bråtbäcken, Bråtbäcken, Vstm</t>
+          <t>Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520967</v>
+        <v>521036</v>
       </c>
       <c r="R20" t="n">
-        <v>6625775</v>
+        <v>6625624</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2830,19 +2839,14 @@
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:18</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2851,23 +2855,19 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -2412,7 +2412,7 @@
         <v>130112840</v>
       </c>
       <c r="B17" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>130112687</v>
       </c>
       <c r="B18" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>130116668</v>
       </c>
       <c r="B20" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>130129396</v>
       </c>
       <c r="B24" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>130112362</v>
       </c>
       <c r="B25" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>130113009</v>
       </c>
       <c r="B26" t="n">
-        <v>105987</v>
+        <v>105990</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>130112471</v>
       </c>
       <c r="B27" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -2303,7 +2303,7 @@
         <v>130116665</v>
       </c>
       <c r="B16" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>130112840</v>
       </c>
       <c r="B17" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>130112687</v>
       </c>
       <c r="B18" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2642,53 +2642,60 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130112479</v>
+        <v>130116668</v>
       </c>
       <c r="B19" t="n">
-        <v>58198</v>
+        <v>98949</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bråtbäcken, Bråtbäcken, Vstm</t>
+          <t>Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520967</v>
+        <v>521036</v>
       </c>
       <c r="R19" t="n">
-        <v>6625775</v>
+        <v>6625624</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2715,19 +2722,14 @@
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:18</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2736,69 +2738,65 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130116668</v>
+        <v>130116663</v>
       </c>
       <c r="B20" t="n">
-        <v>98923</v>
+        <v>57849</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2806,10 +2804,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521036</v>
+        <v>520982</v>
       </c>
       <c r="R20" t="n">
-        <v>6625624</v>
+        <v>6625625</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2844,18 +2842,12 @@
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>30 plantor</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2874,10 +2866,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130116663</v>
+        <v>130116664</v>
       </c>
       <c r="B21" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2921,10 +2913,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520982</v>
+        <v>520981</v>
       </c>
       <c r="R21" t="n">
-        <v>6625625</v>
+        <v>6625634</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2983,10 +2975,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130116664</v>
+        <v>130116662</v>
       </c>
       <c r="B22" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,10 +3022,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520981</v>
+        <v>520980</v>
       </c>
       <c r="R22" t="n">
-        <v>6625634</v>
+        <v>6625623</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3092,10 +3084,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130116662</v>
+        <v>130129396</v>
       </c>
       <c r="B23" t="n">
-        <v>57823</v>
+        <v>91757</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3103,36 +3095,24 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bäckmossen, Vstm</t>
@@ -3175,6 +3155,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3201,10 +3186,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130129396</v>
+        <v>130112362</v>
       </c>
       <c r="B24" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3230,16 +3215,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bäckmossen, Vstm</t>
+          <t>Bäckmossen, Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520980</v>
+        <v>521004</v>
       </c>
       <c r="R24" t="n">
-        <v>6625623</v>
+        <v>6625658</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3269,14 +3257,19 @@
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3285,69 +3278,81 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Ernst Witter</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Ernst Witter</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130112362</v>
+        <v>130113009</v>
       </c>
       <c r="B25" t="n">
-        <v>91731</v>
+        <v>106016</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bäckmossen, Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521004</v>
+        <v>520995</v>
       </c>
       <c r="R25" t="n">
-        <v>6625658</v>
+        <v>6625696</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3376,7 +3381,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3386,7 +3391,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3395,61 +3400,60 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ernst Witter</t>
+          <t>Anneli Sjöstrand</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ernst Witter</t>
+          <t>Anneli Sjöstrand</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130113009</v>
+        <v>130112471</v>
       </c>
       <c r="B26" t="n">
-        <v>105990</v>
+        <v>98949</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3469,7 +3473,7 @@
         <v>6625696</v>
       </c>
       <c r="S26" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3498,7 +3502,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3508,7 +3512,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3535,62 +3539,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130112471</v>
+        <v>130112479</v>
       </c>
       <c r="B27" t="n">
-        <v>98923</v>
+        <v>58224</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bäckmossen, Bäckmossen, Vstm</t>
+          <t>Bråtbäcken, Bråtbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520995</v>
+        <v>520967</v>
       </c>
       <c r="R27" t="n">
-        <v>6625696</v>
+        <v>6625775</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3619,7 +3614,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3629,7 +3624,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3640,16 +3635,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anneli Sjöstrand</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anneli Sjöstrand</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -3189,7 +3189,7 @@
         <v>130112362</v>
       </c>
       <c r="B24" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>130113009</v>
       </c>
       <c r="B25" t="n">
-        <v>106016</v>
+        <v>106017</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>130112471</v>
       </c>
       <c r="B26" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -3189,7 +3189,7 @@
         <v>130112362</v>
       </c>
       <c r="B24" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>130113009</v>
       </c>
       <c r="B25" t="n">
-        <v>106017</v>
+        <v>106018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>130112471</v>
       </c>
       <c r="B26" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -3300,7 +3300,7 @@
         <v>130113009</v>
       </c>
       <c r="B25" t="n">
-        <v>106018</v>
+        <v>106020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>130112471</v>
       </c>
       <c r="B26" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>130112479</v>
       </c>
       <c r="B27" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -3300,7 +3300,7 @@
         <v>130113009</v>
       </c>
       <c r="B25" t="n">
-        <v>106020</v>
+        <v>106024</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>130112471</v>
       </c>
       <c r="B26" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -3659,7 +3659,7 @@
         <v>131307610</v>
       </c>
       <c r="B28" t="n">
-        <v>99018</v>
+        <v>99019</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -1371,7 +1371,7 @@
         <v>129944527</v>
       </c>
       <c r="B8" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>129944905</v>
       </c>
       <c r="B10" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>129944831</v>
       </c>
       <c r="B11" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>129945020</v>
       </c>
       <c r="B12" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129944867</v>
       </c>
       <c r="B14" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>129944637</v>
       </c>
       <c r="B15" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>130116665</v>
       </c>
       <c r="B16" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>130116663</v>
       </c>
       <c r="B20" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>130116664</v>
       </c>
       <c r="B21" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>130116662</v>
       </c>
       <c r="B22" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>131307610</v>
       </c>
       <c r="B28" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -1371,7 +1371,7 @@
         <v>129944527</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>129944905</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>129944831</v>
       </c>
       <c r="B11" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>129945020</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129944867</v>
       </c>
       <c r="B14" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>129944637</v>
       </c>
       <c r="B15" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>130116665</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>130116663</v>
       </c>
       <c r="B20" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>130116664</v>
       </c>
       <c r="B21" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>130116662</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>131307610</v>
       </c>
       <c r="B28" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -1371,7 +1371,7 @@
         <v>129944527</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>129944905</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>129944831</v>
       </c>
       <c r="B11" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>129945020</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129944867</v>
       </c>
       <c r="B14" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>129944637</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>130116665</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>130116663</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>130116664</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>130116662</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>131307610</v>
       </c>
       <c r="B28" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -1371,7 +1371,7 @@
         <v>129944527</v>
       </c>
       <c r="B8" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>129944905</v>
       </c>
       <c r="B10" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>129944831</v>
       </c>
       <c r="B11" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>129945020</v>
       </c>
       <c r="B12" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>129944867</v>
       </c>
       <c r="B14" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>129944637</v>
       </c>
       <c r="B15" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>130116665</v>
       </c>
       <c r="B16" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>130116663</v>
       </c>
       <c r="B20" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>130116664</v>
       </c>
       <c r="B21" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>130116662</v>
       </c>
       <c r="B22" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>131307610</v>
       </c>
       <c r="B28" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -1371,7 +1371,7 @@
         <v>129944527</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>129944905</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>129945020</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>129944637</v>
       </c>
       <c r="B15" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>130116665</v>
       </c>
       <c r="B16" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>130116663</v>
       </c>
       <c r="B20" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>130116664</v>
       </c>
       <c r="B21" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>130116662</v>
       </c>
       <c r="B22" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>131307610</v>
       </c>
       <c r="B28" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -3659,7 +3659,7 @@
         <v>131307610</v>
       </c>
       <c r="B28" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -3659,7 +3659,7 @@
         <v>131307610</v>
       </c>
       <c r="B28" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -3659,7 +3659,7 @@
         <v>131307610</v>
       </c>
       <c r="B28" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -3659,7 +3659,7 @@
         <v>131307610</v>
       </c>
       <c r="B28" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -3659,7 +3659,7 @@
         <v>131307610</v>
       </c>
       <c r="B28" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -675,59 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129944723</v>
+        <v>130112362</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bäckmossen, Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521067</v>
+        <v>521004</v>
       </c>
       <c r="R2" t="n">
-        <v>6625633</v>
+        <v>6625658</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,22 +743,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,77 +767,64 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Ernst Witter</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Ernst Witter</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129944923</v>
+        <v>130129396</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bäckmossen, Bäckmossen, Vstm</t>
+          <t>Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520994</v>
+        <v>520980</v>
       </c>
       <c r="R3" t="n">
-        <v>6625611</v>
+        <v>6625623</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,22 +851,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,57 +876,62 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129944586</v>
+        <v>129944527</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bäckmossen, Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521079</v>
+        <v>521096</v>
       </c>
       <c r="R4" t="n">
-        <v>6625635</v>
+        <v>6625627</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,42 +1000,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129944799</v>
+        <v>129944637</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1068,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521050</v>
+        <v>521069</v>
       </c>
       <c r="R5" t="n">
-        <v>6625624</v>
+        <v>6625634</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,47 +1112,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129944648</v>
+        <v>129944905</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1189,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521069</v>
+        <v>520994</v>
       </c>
       <c r="R6" t="n">
-        <v>6625634</v>
+        <v>6625626</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1187,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1197,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,45 +1224,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129944497</v>
+        <v>129945020</v>
       </c>
       <c r="B7" t="n">
-        <v>98920</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bäckmossen, Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521096</v>
+        <v>520980</v>
       </c>
       <c r="R7" t="n">
-        <v>6625627</v>
+        <v>6625624</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1341,7 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,14 +1340,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129944527</v>
+        <v>130116662</v>
       </c>
       <c r="B8" t="n">
-        <v>57889</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1396,22 +1368,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bäckmossen, Bäckmossen, Vstm</t>
+          <t>Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521096</v>
+        <v>520980</v>
       </c>
       <c r="R8" t="n">
-        <v>6625627</v>
+        <v>6625623</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,22 +1417,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,44 +1437,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129944883</v>
+        <v>130116663</v>
       </c>
       <c r="B9" t="n">
-        <v>98920</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1513,26 +1482,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bäckmossen, Bäckmossen, Vstm</t>
+          <t>Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521009</v>
+        <v>520982</v>
       </c>
       <c r="R9" t="n">
-        <v>6625622</v>
+        <v>6625625</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,22 +1526,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:18</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:18</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,26 +1546,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129944905</v>
+        <v>130116664</v>
       </c>
       <c r="B10" t="n">
-        <v>57889</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1629,22 +1586,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bäckmossen, Bäckmossen, Vstm</t>
+          <t>Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520994</v>
+        <v>520981</v>
       </c>
       <c r="R10" t="n">
-        <v>6625626</v>
+        <v>6625634</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,22 +1635,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,65 +1655,72 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129944831</v>
+        <v>130116665</v>
       </c>
       <c r="B11" t="n">
-        <v>58050</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bäckmossen, Bäckmossen, Vstm</t>
+          <t>Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521008</v>
+        <v>520998</v>
       </c>
       <c r="R11" t="n">
-        <v>6625737</v>
+        <v>6625749</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1783,22 +1744,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:11</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:11</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,48 +1760,43 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129945020</v>
+        <v>130112479</v>
       </c>
       <c r="B12" t="n">
-        <v>57889</v>
+        <v>58327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1858,29 +1804,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bäckmossen, Bäckmossen, Vstm</t>
+          <t>Bråtbäcken, Bråtbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520980</v>
+        <v>520967</v>
       </c>
       <c r="R12" t="n">
-        <v>6625624</v>
+        <v>6625775</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1904,22 +1846,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,63 +1872,59 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129944853</v>
+        <v>129944831</v>
       </c>
       <c r="B13" t="n">
-        <v>98920</v>
+        <v>58114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1995,13 +1933,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521037</v>
+        <v>521008</v>
       </c>
       <c r="R13" t="n">
-        <v>6625622</v>
+        <v>6625737</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2051,16 +1989,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2070,7 +2013,7 @@
         <v>129944867</v>
       </c>
       <c r="B14" t="n">
-        <v>58050</v>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2188,50 +2131,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129944637</v>
+        <v>129944497</v>
       </c>
       <c r="B15" t="n">
-        <v>57889</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bäckmossen, Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521069</v>
+        <v>521096</v>
       </c>
       <c r="R15" t="n">
-        <v>6625634</v>
+        <v>6625627</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2263,7 +2201,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2273,7 +2211,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2300,57 +2238,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130116665</v>
+        <v>129944586</v>
       </c>
       <c r="B16" t="n">
-        <v>57889</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bäckmossen, Vstm</t>
+          <t>Bäckmossen, Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520998</v>
+        <v>521079</v>
       </c>
       <c r="R16" t="n">
-        <v>6625749</v>
+        <v>6625635</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2377,12 +2303,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,22 +2333,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130112840</v>
+        <v>129944648</v>
       </c>
       <c r="B17" t="n">
-        <v>98949</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2439,12 +2375,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2458,13 +2394,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520973</v>
+        <v>521069</v>
       </c>
       <c r="R17" t="n">
-        <v>6625697</v>
+        <v>6625634</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2488,22 +2424,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,31 +2450,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130112687</v>
+        <v>129944723</v>
       </c>
       <c r="B18" t="n">
-        <v>98949</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2563,17 +2494,31 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bäckmossen, Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521082</v>
+        <v>521067</v>
       </c>
       <c r="R18" t="n">
-        <v>6625605</v>
+        <v>6625633</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2600,22 +2545,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2630,22 +2575,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ernst Witter</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ernst Witter</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130116668</v>
+        <v>129944799</v>
       </c>
       <c r="B19" t="n">
-        <v>98949</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2672,24 +2617,21 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bäckmossen, Vstm</t>
+          <t>Bäckmossen, Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521036</v>
+        <v>521050</v>
       </c>
       <c r="R19" t="n">
         <v>6625624</v>
@@ -2719,17 +2661,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>30 plantor</t>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,76 +2685,77 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130116663</v>
+        <v>129944853</v>
       </c>
       <c r="B20" t="n">
-        <v>57889</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bäckmossen, Vstm</t>
+          <t>Bäckmossen, Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520982</v>
+        <v>521037</v>
       </c>
       <c r="R20" t="n">
-        <v>6625625</v>
+        <v>6625622</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2834,12 +2782,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2854,44 +2812,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130116664</v>
+        <v>129944883</v>
       </c>
       <c r="B21" t="n">
-        <v>57889</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2899,24 +2857,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bäckmossen, Vstm</t>
+          <t>Bäckmossen, Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520981</v>
+        <v>521009</v>
       </c>
       <c r="R21" t="n">
-        <v>6625634</v>
+        <v>6625622</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2943,12 +2903,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2963,44 +2933,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130116662</v>
+        <v>129944923</v>
       </c>
       <c r="B22" t="n">
-        <v>57889</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3008,24 +2978,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bäckmossen, Vstm</t>
+          <t>Bäckmossen, Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520980</v>
+        <v>520994</v>
       </c>
       <c r="R22" t="n">
-        <v>6625623</v>
+        <v>6625611</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3052,12 +3024,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3072,57 +3054,71 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130129396</v>
+        <v>130112471</v>
       </c>
       <c r="B23" t="n">
-        <v>91757</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bäckmossen, Vstm</t>
+          <t>Bäckmossen, Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520980</v>
+        <v>520995</v>
       </c>
       <c r="R23" t="n">
-        <v>6625623</v>
+        <v>6625696</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3152,14 +3148,19 @@
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3174,60 +3175,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Anneli Sjöstrand</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Mattias Drejby</t>
+          <t>Anneli Sjöstrand</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130112362</v>
+        <v>130112687</v>
       </c>
       <c r="B24" t="n">
-        <v>91759</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bäckmossen, Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>521004</v>
+        <v>521082</v>
       </c>
       <c r="R24" t="n">
-        <v>6625658</v>
+        <v>6625605</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3278,7 +3276,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3297,37 +3294,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130113009</v>
+        <v>130112840</v>
       </c>
       <c r="B25" t="n">
-        <v>106041</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3346,13 +3343,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520995</v>
+        <v>520973</v>
       </c>
       <c r="R25" t="n">
-        <v>6625696</v>
+        <v>6625697</v>
       </c>
       <c r="S25" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3381,7 +3378,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3391,7 +3388,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3402,26 +3399,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anneli Sjöstrand</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anneli Sjöstrand</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130112471</v>
+        <v>130116668</v>
       </c>
       <c r="B26" t="n">
-        <v>98974</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3448,7 +3450,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3456,21 +3458,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bäckmossen, Bäckmossen, Vstm</t>
+          <t>Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520995</v>
+        <v>521036</v>
       </c>
       <c r="R26" t="n">
-        <v>6625696</v>
+        <v>6625624</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3500,19 +3500,14 @@
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:16</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:16</t>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3521,71 +3516,81 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anneli Sjöstrand</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anneli Sjöstrand</t>
+          <t>Mattias Drejby</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130112479</v>
+        <v>131307610</v>
       </c>
       <c r="B27" t="n">
-        <v>58256</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bråtbäcken, Bråtbäcken, Vstm</t>
+          <t>Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520967</v>
+        <v>521051</v>
       </c>
       <c r="R27" t="n">
-        <v>6625775</v>
+        <v>6625617</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3607,24 +3612,19 @@
           <t>Ramsberg</t>
         </is>
       </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>T-Lin-0017</t>
+        </is>
+      </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:18</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:18</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3635,63 +3635,62 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Sofia Lund</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131307610</v>
+        <v>130113009</v>
       </c>
       <c r="B28" t="n">
-        <v>99044</v>
+        <v>106243</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3701,17 +3700,17 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bäckmossen, Vstm</t>
+          <t>Bäckmossen, Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521051</v>
+        <v>520995</v>
       </c>
       <c r="R28" t="n">
-        <v>6625617</v>
+        <v>6625696</v>
       </c>
       <c r="S28" t="n">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3733,19 +3732,24 @@
           <t>Ramsberg</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>T-Lin-0017</t>
-        </is>
-      </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3760,19 +3764,15 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Sofia Lund</t>
+          <t>Anneli Sjöstrand</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Anneli Sjöstrand</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130112362</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130129396</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944527</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944637</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,6 +1246,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944905</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1337,6 +1367,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129945020</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1446,6 +1481,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130116662</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1555,6 +1595,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130116663</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1664,6 +1709,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130116664</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1773,6 +1823,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130116665</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1890,6 +1945,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130112479</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2007,6 +2067,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944831</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2128,6 +2193,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944867</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2235,6 +2305,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944497</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2342,6 +2417,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944586</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2463,6 +2543,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944648</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2584,6 +2669,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944723</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2700,6 +2790,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944799</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2821,6 +2916,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944853</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2942,6 +3042,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944883</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3063,6 +3168,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944923</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3184,6 +3294,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130112471</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3291,6 +3406,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130112687</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3417,6 +3537,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130112840</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3532,6 +3657,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130116668</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3652,6 +3782,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131307610</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3773,8 +3908,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130113009</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ27"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3665,42 +3665,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130113009</v>
+        <v>131307610</v>
       </c>
       <c r="B27" t="n">
-        <v>106243</v>
+        <v>99274</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3710,17 +3710,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bäckmossen, Bäckmossen, Vstm</t>
+          <t>Bäckmossen, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520995</v>
+        <v>521051</v>
       </c>
       <c r="R27" t="n">
-        <v>6625696</v>
+        <v>6625617</v>
       </c>
       <c r="S27" t="n">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3742,24 +3742,19 @@
           <t>Ramsberg</t>
         </is>
       </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>T-Lin-0017</t>
+        </is>
+      </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:55</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:55</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3774,16 +3769,146 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131307610</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130113009</v>
+      </c>
+      <c r="B28" t="n">
+        <v>106243</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bäckmossen, Bäckmossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>520995</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6625696</v>
+      </c>
+      <c r="S28" t="n">
+        <v>36</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
           <t>Anneli Sjöstrand</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
+      <c r="AX28" t="inlineStr">
         <is>
           <t>Anneli Sjöstrand</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
-      <c r="AZ27" t="inlineStr">
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/130113009</t>
         </is>
@@ -3817,6 +3942,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -3668,7 +3668,7 @@
         <v>131307610</v>
       </c>
       <c r="B27" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -3668,7 +3668,7 @@
         <v>131307610</v>
       </c>
       <c r="B27" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -3668,7 +3668,7 @@
         <v>131307610</v>
       </c>
       <c r="B27" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -3668,7 +3668,7 @@
         <v>131307610</v>
       </c>
       <c r="B27" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -3668,7 +3668,7 @@
         <v>131307610</v>
       </c>
       <c r="B27" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -3668,7 +3668,7 @@
         <v>131307610</v>
       </c>
       <c r="B27" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -3668,7 +3668,7 @@
         <v>131307610</v>
       </c>
       <c r="B27" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -3668,7 +3668,7 @@
         <v>131307610</v>
       </c>
       <c r="B27" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -3668,7 +3668,7 @@
         <v>131307610</v>
       </c>
       <c r="B27" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -3668,7 +3668,7 @@
         <v>131307610</v>
       </c>
       <c r="B27" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 54241-2025 artfynd.xlsx
+++ b/artfynd/A 54241-2025 artfynd.xlsx
@@ -3668,7 +3668,7 @@
         <v>131307610</v>
       </c>
       <c r="B27" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
